--- a/v3/OG0021/OG0021_DevSpec.xlsx
+++ b/v3/OG0021/OG0021_DevSpec.xlsx
@@ -1279,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>forest.</t>
+          <t>the forest.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>into</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>into</t>
+          <t>walks</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>walks</t>
+          <t>Milo</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1733,21 +1733,25 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>OG0021_V3_Q04</t>
+          <t>OG0021_V3_Q05</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Milo</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1758,21 +1762,25 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>해결 이후 감정을 슬픈 장면에 적용합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1782,23 +1790,23 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>해결 이후 감정을 슬픈 장면에 적용합니다.</t>
+          <t>부정 감정은 파악했지만 슬픔과 분노를 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -1810,53 +1818,49 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>proud</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>부정 감정은 파악했지만 슬픔과 분노를 혼동합니다.</t>
+          <t>결말의 자신감을 현재 감정으로 혼동합니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OG0021_V3_Q05</t>
+          <t>OG0021_V3_Q06</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>proud</t>
+          <t>Maybe my color is inside me!</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>결말의 자신감을 현재 감정으로 혼동합니다.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1866,21 +1870,25 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Maybe my color is inside me!</t>
+          <t>I need the butterfly's color.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>외부에서 색을 얻으려는 초반 생각에 머무릅니다.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1890,23 +1898,23 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>I need the butterfly's color.</t>
+          <t>I should stop looking.</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>외부에서 색을 얻으려는 초반 생각에 머무릅니다.</t>
+          <t>슬픈 반응과 깨달음을 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -1918,49 +1926,21 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>I should stop looking.</t>
+          <t>The pond is my home.</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>슬픈 반응과 깨달음을 혼동합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>OG0021_V3_Q06</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>The pond is my home.</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>장면의 배경 단서를 내적 깨달음으로 오해합니다.</t>
         </is>
@@ -1977,7 +1957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2481,11 +2461,11 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>the forest.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -2505,29 +2485,29 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>OG0021_V3_Q04</t>
+          <t>OG0021_V3_Q05</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>forest.</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2.5</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>exact_position</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>5</v>
+          <t>option_score</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Actor/action/result word order.</t>
+          <t>Correct reaction/emotion.</t>
         </is>
       </c>
     </row>
@@ -2539,11 +2519,11 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -2551,12 +2531,12 @@
         </is>
       </c>
       <c r="E19" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Correct reaction/emotion.</t>
+          <t>해결 이후 감정을 슬픈 장면에 적용합니다.</t>
         </is>
       </c>
     </row>
@@ -2568,11 +2548,11 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -2585,7 +2565,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>해결 이후 감정을 슬픈 장면에 적용합니다.</t>
+          <t>부정 감정은 파악했지만 슬픔과 분노를 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -2597,11 +2577,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -2614,23 +2594,23 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>부정 감정은 파악했지만 슬픔과 분노를 혼동합니다.</t>
+          <t>결말의 자신감을 현재 감정으로 혼동합니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>OG0021_V3_Q05</t>
+          <t>OG0021_V3_Q06</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2618,12 @@
         </is>
       </c>
       <c r="E22" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>결말의 자신감을 현재 감정으로 혼동합니다.</t>
+          <t>Correct internal response.</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2635,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -2667,12 +2647,12 @@
         </is>
       </c>
       <c r="E23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Correct internal response.</t>
+          <t>외부에서 색을 얻으려는 초반 생각에 머무릅니다.</t>
         </is>
       </c>
     </row>
@@ -2684,11 +2664,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -2701,7 +2681,7 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>외부에서 색을 얻으려는 초반 생각에 머무릅니다.</t>
+          <t>슬픈 반응과 깨달음을 혼동합니다.</t>
         </is>
       </c>
     </row>
@@ -2713,11 +2693,11 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -2729,35 +2709,6 @@
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>슬픈 반응과 깨달음을 혼동합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>OG0021_V3_Q06</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>option_score</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>장면의 배경 단서를 내적 깨달음으로 오해합니다.</t>
         </is>
